--- a/Daily_Report/Top 7 broker List with its Turnover 2024-07-17.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-07-17.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="278">
   <si>
     <t>Date: 2024-07-17</t>
   </si>
@@ -62,7 +62,10 @@
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
-    <t>Kohinoor Investment and Securities Pvt.Ltd</t>
+    <t>Imperial Securities Co .Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
     <t>Dynamic Money Managers Securities Pvt.Ltd</t>
@@ -71,19 +74,19 @@
     <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
     <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
   </si>
   <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Investment Management Nepal Pvt. Ltd.</t>
-  </si>
-  <si>
     <t>58</t>
   </si>
   <si>
-    <t>35</t>
+    <t>45</t>
+  </si>
+  <si>
+    <t>34</t>
   </si>
   <si>
     <t>44</t>
@@ -92,76 +95,73 @@
     <t>49</t>
   </si>
   <si>
+    <t>42</t>
+  </si>
+  <si>
     <t>38</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>1,500,605,570.3</t>
-  </si>
-  <si>
-    <t>1,202,236,374.5</t>
-  </si>
-  <si>
-    <t>960,251,245.0</t>
-  </si>
-  <si>
-    <t>945,221,048.82</t>
-  </si>
-  <si>
-    <t>838,258,586.09</t>
-  </si>
-  <si>
-    <t>831,658,639.9</t>
-  </si>
-  <si>
-    <t>787,383,981.5</t>
-  </si>
-  <si>
-    <t>959,553,586.1</t>
-  </si>
-  <si>
-    <t>223,410,444.8</t>
-  </si>
-  <si>
-    <t>770,692,128.4</t>
-  </si>
-  <si>
-    <t>404,633,024.5</t>
-  </si>
-  <si>
-    <t>270,458,966.8</t>
-  </si>
-  <si>
-    <t>593,161,289.0</t>
-  </si>
-  <si>
-    <t>142,729,870.9</t>
-  </si>
-  <si>
-    <t>541,051,984.2</t>
-  </si>
-  <si>
-    <t>978,825,929.7</t>
-  </si>
-  <si>
-    <t>189,559,116.6</t>
-  </si>
-  <si>
-    <t>540,588,024.32</t>
-  </si>
-  <si>
-    <t>567,799,619.29</t>
-  </si>
-  <si>
-    <t>238,497,350.9</t>
-  </si>
-  <si>
-    <t>644,654,110.6</t>
+    <t>1,566,660,865.1</t>
+  </si>
+  <si>
+    <t>912,312,736.6</t>
+  </si>
+  <si>
+    <t>858,779,407.31</t>
+  </si>
+  <si>
+    <t>833,183,754.2</t>
+  </si>
+  <si>
+    <t>819,913,557.42</t>
+  </si>
+  <si>
+    <t>721,807,751.89</t>
+  </si>
+  <si>
+    <t>703,876,298.5</t>
+  </si>
+  <si>
+    <t>790,263,946.6</t>
+  </si>
+  <si>
+    <t>511,487,204.5</t>
+  </si>
+  <si>
+    <t>473,813,154.8</t>
+  </si>
+  <si>
+    <t>421,534,413.9</t>
+  </si>
+  <si>
+    <t>435,176,608.8</t>
+  </si>
+  <si>
+    <t>347,757,627.94</t>
+  </si>
+  <si>
+    <t>314,151,400.0</t>
+  </si>
+  <si>
+    <t>776,396,918.5</t>
+  </si>
+  <si>
+    <t>400,825,532.1</t>
+  </si>
+  <si>
+    <t>384,966,252.51</t>
+  </si>
+  <si>
+    <t>411,649,340.3</t>
+  </si>
+  <si>
+    <t>384,736,948.62</t>
+  </si>
+  <si>
+    <t>374,050,123.95</t>
+  </si>
+  <si>
+    <t>389,724,898.5</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,376 +179,337 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>MMKJL</t>
-  </si>
-  <si>
-    <t>318,470,135.2</t>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>69,643,225.5</t>
+  </si>
+  <si>
+    <t>SHINE</t>
+  </si>
+  <si>
+    <t>64,129,547.5</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>28,494,724.4</t>
   </si>
   <si>
     <t>MEN</t>
   </si>
   <si>
-    <t>79,336,336.9</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>64,337,760.5</t>
-  </si>
-  <si>
-    <t>SHINE</t>
-  </si>
-  <si>
-    <t>58,136,692.1</t>
-  </si>
-  <si>
-    <t>KRBL</t>
-  </si>
-  <si>
-    <t>32,544,933.8</t>
-  </si>
-  <si>
-    <t>TAMOR</t>
-  </si>
-  <si>
-    <t>38,431,376.0</t>
+    <t>28,335,313.9</t>
+  </si>
+  <si>
+    <t>EDBL</t>
+  </si>
+  <si>
+    <t>25,722,705.9</t>
+  </si>
+  <si>
+    <t>40,238,345.2</t>
+  </si>
+  <si>
+    <t>SHEL</t>
+  </si>
+  <si>
+    <t>24,815,363.1</t>
+  </si>
+  <si>
+    <t>HDHPC</t>
+  </si>
+  <si>
+    <t>15,246,490.0</t>
+  </si>
+  <si>
+    <t>EBL</t>
+  </si>
+  <si>
+    <t>11,128,704.5</t>
+  </si>
+  <si>
+    <t>AHPC</t>
+  </si>
+  <si>
+    <t>9,766,218.9</t>
+  </si>
+  <si>
+    <t>MKCL</t>
+  </si>
+  <si>
+    <t>14,428,370.0</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>10,622,774.3</t>
+  </si>
+  <si>
+    <t>10,593,749.8</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>10,343,522.3</t>
+  </si>
+  <si>
+    <t>HEI</t>
+  </si>
+  <si>
+    <t>10,243,682.6</t>
+  </si>
+  <si>
+    <t>SBI</t>
+  </si>
+  <si>
+    <t>44,634,062.0</t>
+  </si>
+  <si>
+    <t>SCB</t>
+  </si>
+  <si>
+    <t>25,878,510.8</t>
+  </si>
+  <si>
+    <t>NLICL</t>
+  </si>
+  <si>
+    <t>25,553,497.8</t>
+  </si>
+  <si>
+    <t>SPIL</t>
+  </si>
+  <si>
+    <t>18,244,410.89</t>
+  </si>
+  <si>
+    <t>SWBBL</t>
+  </si>
+  <si>
+    <t>17,878,673.5</t>
   </si>
   <si>
     <t>NICL</t>
   </si>
   <si>
-    <t>15,439,654.0</t>
-  </si>
-  <si>
-    <t>NICLBSL</t>
-  </si>
-  <si>
-    <t>12,980,700.0</t>
-  </si>
-  <si>
-    <t>SHEL</t>
-  </si>
-  <si>
-    <t>12,371,134.2</t>
-  </si>
-  <si>
-    <t>SARBTM</t>
-  </si>
-  <si>
-    <t>10,279,875.0</t>
-  </si>
-  <si>
-    <t>NLICL</t>
-  </si>
-  <si>
-    <t>494,628,178.0</t>
-  </si>
-  <si>
-    <t>NADEP</t>
-  </si>
-  <si>
-    <t>51,729,210.0</t>
-  </si>
-  <si>
-    <t>SBI</t>
-  </si>
-  <si>
-    <t>28,637,512.5</t>
-  </si>
-  <si>
-    <t>28,456,201.5</t>
-  </si>
-  <si>
-    <t>SCB</t>
-  </si>
-  <si>
-    <t>18,679,059.8</t>
+    <t>27,428,854.7</t>
+  </si>
+  <si>
+    <t>RLFL</t>
+  </si>
+  <si>
+    <t>11,125,548.5</t>
+  </si>
+  <si>
+    <t>PRIN</t>
+  </si>
+  <si>
+    <t>10,123,907.6</t>
+  </si>
+  <si>
+    <t>9,796,502.3</t>
+  </si>
+  <si>
+    <t>CHCL</t>
+  </si>
+  <si>
+    <t>9,352,972.8</t>
+  </si>
+  <si>
+    <t>10,029,532.8</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>9,578,345.8</t>
+  </si>
+  <si>
+    <t>SANIMA</t>
+  </si>
+  <si>
+    <t>7,763,815.4</t>
   </si>
   <si>
     <t>SONA</t>
   </si>
   <si>
-    <t>78,799,274.7</t>
-  </si>
-  <si>
-    <t>NMB</t>
-  </si>
-  <si>
-    <t>36,880,262.5</t>
+    <t>7,726,370.5</t>
+  </si>
+  <si>
+    <t>7,155,056.8</t>
+  </si>
+  <si>
+    <t>RURU</t>
+  </si>
+  <si>
+    <t>34,730,308.29</t>
+  </si>
+  <si>
+    <t>10,839,662.8</t>
+  </si>
+  <si>
+    <t>9,162,994.5</t>
+  </si>
+  <si>
+    <t>JFL</t>
+  </si>
+  <si>
+    <t>8,918,218.4</t>
+  </si>
+  <si>
+    <t>SFCL</t>
+  </si>
+  <si>
+    <t>7,167,843.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>57,291,731.1</t>
+  </si>
+  <si>
+    <t>26,355,134.6</t>
+  </si>
+  <si>
+    <t>25,763,924.9</t>
+  </si>
+  <si>
+    <t>23,693,346.0</t>
+  </si>
+  <si>
+    <t>FOWAD</t>
+  </si>
+  <si>
+    <t>22,559,949.2</t>
+  </si>
+  <si>
+    <t>11,975,850.6</t>
+  </si>
+  <si>
+    <t>11,080,764.0</t>
+  </si>
+  <si>
+    <t>9,713,304.69</t>
   </si>
   <si>
     <t>TRH</t>
   </si>
   <si>
-    <t>27,384,183.5</t>
-  </si>
-  <si>
-    <t>23,612,528.4</t>
-  </si>
-  <si>
-    <t>LLBS</t>
-  </si>
-  <si>
-    <t>21,448,700.0</t>
-  </si>
-  <si>
-    <t>KKHC</t>
-  </si>
-  <si>
-    <t>64,377,000.0</t>
+    <t>9,406,179.5</t>
+  </si>
+  <si>
+    <t>SHL</t>
+  </si>
+  <si>
+    <t>9,124,098.0</t>
   </si>
   <si>
     <t>API</t>
   </si>
   <si>
-    <t>33,870,111.5</t>
-  </si>
-  <si>
-    <t>29,638,890.0</t>
-  </si>
-  <si>
-    <t>RIDI</t>
-  </si>
-  <si>
-    <t>5,718,249.6</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>5,433,460.5</t>
-  </si>
-  <si>
-    <t>ILI</t>
-  </si>
-  <si>
-    <t>113,060,151.0</t>
-  </si>
-  <si>
-    <t>SIKLES</t>
-  </si>
-  <si>
-    <t>59,552,460.0</t>
-  </si>
-  <si>
-    <t>SAHAS</t>
-  </si>
-  <si>
-    <t>46,061,450.0</t>
-  </si>
-  <si>
-    <t>CITY</t>
-  </si>
-  <si>
-    <t>27,806,100.0</t>
-  </si>
-  <si>
-    <t>BPCL</t>
-  </si>
-  <si>
-    <t>27,405,762.0</t>
-  </si>
-  <si>
-    <t>27,360,000.0</t>
-  </si>
-  <si>
-    <t>23,513,573.3</t>
-  </si>
-  <si>
-    <t>13,731,300.0</t>
-  </si>
-  <si>
-    <t>RNLI</t>
-  </si>
-  <si>
-    <t>11,517,300.4</t>
-  </si>
-  <si>
-    <t>AHL</t>
-  </si>
-  <si>
-    <t>8,407,340.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>KBL</t>
-  </si>
-  <si>
-    <t>82,600,541.5</t>
-  </si>
-  <si>
-    <t>46,988,533.6</t>
-  </si>
-  <si>
-    <t>27,707,417.0</t>
-  </si>
-  <si>
-    <t>CHDC</t>
-  </si>
-  <si>
-    <t>23,288,456.0</t>
-  </si>
-  <si>
-    <t>FOWAD</t>
-  </si>
-  <si>
-    <t>22,545,399.2</t>
-  </si>
-  <si>
-    <t>311,180,575.0</t>
-  </si>
-  <si>
-    <t>236,581,963.0</t>
+    <t>16,152,542.3</t>
+  </si>
+  <si>
+    <t>14,821,245.7</t>
+  </si>
+  <si>
+    <t>11,211,391.4</t>
+  </si>
+  <si>
+    <t>10,848,939.9</t>
+  </si>
+  <si>
+    <t>SGIC</t>
+  </si>
+  <si>
+    <t>7,535,444.4</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>29,053,429.1</t>
+  </si>
+  <si>
+    <t>20,308,889.7</t>
+  </si>
+  <si>
+    <t>20,059,380.39</t>
+  </si>
+  <si>
+    <t>19,335,806.1</t>
+  </si>
+  <si>
+    <t>13,152,363.5</t>
+  </si>
+  <si>
+    <t>23,782,353.0</t>
+  </si>
+  <si>
+    <t>UPPER</t>
+  </si>
+  <si>
+    <t>12,450,405.3</t>
+  </si>
+  <si>
+    <t>11,488,763.1</t>
+  </si>
+  <si>
+    <t>9,391,058.0</t>
+  </si>
+  <si>
+    <t>7,792,133.3</t>
+  </si>
+  <si>
+    <t>10,004,525.19</t>
+  </si>
+  <si>
+    <t>8,882,400.4</t>
+  </si>
+  <si>
+    <t>IGI</t>
+  </si>
+  <si>
+    <t>8,645,320.1</t>
+  </si>
+  <si>
+    <t>NABIL</t>
+  </si>
+  <si>
+    <t>8,448,740.0</t>
   </si>
   <si>
     <t>MFIL</t>
   </si>
   <si>
-    <t>76,584,422.59</t>
-  </si>
-  <si>
-    <t>MKHL</t>
-  </si>
-  <si>
-    <t>59,606,564.4</t>
-  </si>
-  <si>
-    <t>MHCL</t>
-  </si>
-  <si>
-    <t>41,223,971.9</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>17,054,281.89</t>
-  </si>
-  <si>
-    <t>SPIL</t>
-  </si>
-  <si>
-    <t>10,419,974.0</t>
-  </si>
-  <si>
-    <t>SWBBL</t>
-  </si>
-  <si>
-    <t>9,537,292.0</t>
-  </si>
-  <si>
-    <t>RADHI</t>
-  </si>
-  <si>
-    <t>7,758,270.0</t>
-  </si>
-  <si>
-    <t>6,387,103.0</t>
-  </si>
-  <si>
-    <t>SPDL</t>
-  </si>
-  <si>
-    <t>145,556,071.0</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>52,747,076.0</t>
-  </si>
-  <si>
-    <t>HDHPC</t>
-  </si>
-  <si>
-    <t>51,449,426.1</t>
-  </si>
-  <si>
-    <t>42,247,397.0</t>
-  </si>
-  <si>
-    <t>23,730,338.0</t>
-  </si>
-  <si>
-    <t>BEDC</t>
-  </si>
-  <si>
-    <t>236,210,879.0</t>
-  </si>
-  <si>
-    <t>SRLI</t>
-  </si>
-  <si>
-    <t>82,197,393.0</t>
-  </si>
-  <si>
-    <t>PPL</t>
-  </si>
-  <si>
-    <t>55,568,364.7</t>
-  </si>
-  <si>
-    <t>18,415,720.89</t>
-  </si>
-  <si>
-    <t>UHEWA</t>
-  </si>
-  <si>
-    <t>14,855,379.0</t>
-  </si>
-  <si>
-    <t>GBIME</t>
-  </si>
-  <si>
-    <t>16,262,966.1</t>
-  </si>
-  <si>
-    <t>OHL</t>
-  </si>
-  <si>
-    <t>10,062,877.19</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>8,544,068.0</t>
-  </si>
-  <si>
-    <t>6,556,945.0</t>
-  </si>
-  <si>
-    <t>6,520,327.0</t>
-  </si>
-  <si>
-    <t>530,237,819.0</t>
-  </si>
-  <si>
-    <t>NIFRA</t>
-  </si>
-  <si>
-    <t>35,682,170.0</t>
-  </si>
-  <si>
-    <t>LBBL</t>
-  </si>
-  <si>
-    <t>17,323,408.39</t>
-  </si>
-  <si>
-    <t>HDL</t>
-  </si>
-  <si>
-    <t>9,670,115.4</t>
-  </si>
-  <si>
-    <t>HEI</t>
-  </si>
-  <si>
-    <t>6,064,812.0</t>
+    <t>7,868,856.0</t>
+  </si>
+  <si>
+    <t>52,600,981.6</t>
+  </si>
+  <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>10,599,077.3</t>
+  </si>
+  <si>
+    <t>BARUN</t>
+  </si>
+  <si>
+    <t>8,951,269.3</t>
+  </si>
+  <si>
+    <t>8,782,104.0</t>
+  </si>
+  <si>
+    <t>7,594,971.0</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -566,109 +527,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>541,654,697.5</t>
-  </si>
-  <si>
-    <t>495,920,738.6</t>
-  </si>
-  <si>
-    <t>323,572,714.2</t>
-  </si>
-  <si>
-    <t>264,537,357.0</t>
-  </si>
-  <si>
-    <t>235,926,509.5</t>
+    <t>235,581,637.7</t>
+  </si>
+  <si>
+    <t>227,149,890.1</t>
+  </si>
+  <si>
+    <t>203,539,648.2</t>
+  </si>
+  <si>
+    <t>202,756,487.7</t>
+  </si>
+  <si>
+    <t>194,444,136.4</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>3,246,598,222.1</t>
+    <t>3,696,100,452.5</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>3,061,099,481.3</t>
+    <t>2,566,390,808.55</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>1,052,441,226.8</t>
+    <t>1,236,267,575.3</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>986,304,747.1</t>
+    <t>998,796,446.1</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>864,121,381.1</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>852,204,607.1</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>739,646,245.9</t>
+    <t>782,639,432.9</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>625,850,178.4</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>359,348,281.6</t>
+  </si>
+  <si>
+    <t>Hotels And Tourism</t>
+  </si>
+  <si>
+    <t>273,986,131.5</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>258,511,530.4</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>628,990,597.5</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>517,717,698.1</t>
-  </si>
-  <si>
-    <t>Hotels And Tourism</t>
-  </si>
-  <si>
-    <t>253,451,000.6</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>223,667,627.7</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>136,807,518.1</t>
+    <t>207,229,411.2</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>41,453,957.4</t>
+    <t>93,025,173.6</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>34,445,367.9</t>
+    <t>68,016,839.59</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>17,339,770.57</t>
+    <t>22,213,903.42</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>3,802,892.0</t>
+    <t>6,768,567.3</t>
   </si>
   <si>
     <t>Total</t>
@@ -680,214 +641,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>409,025,564.0</t>
-  </si>
-  <si>
-    <t>189,369,591.6</t>
-  </si>
-  <si>
-    <t>170,200,384.8</t>
-  </si>
-  <si>
-    <t>74,953,881.8</t>
-  </si>
-  <si>
-    <t>48,090,586.8</t>
-  </si>
-  <si>
-    <t>76,525,493.7</t>
-  </si>
-  <si>
-    <t>54,853,091.8</t>
-  </si>
-  <si>
-    <t>29,801,438.0</t>
-  </si>
-  <si>
-    <t>19,046,897.0</t>
-  </si>
-  <si>
-    <t>14,293,509.6</t>
-  </si>
-  <si>
-    <t>496,087,256.6</t>
-  </si>
-  <si>
-    <t>67,458,507.8</t>
-  </si>
-  <si>
-    <t>65,952,948.0</t>
-  </si>
-  <si>
-    <t>63,454,934.6</t>
-  </si>
-  <si>
-    <t>26,602,284.1</t>
-  </si>
-  <si>
-    <t>146,992,865.1</t>
-  </si>
-  <si>
-    <t>52,908,675.1</t>
-  </si>
-  <si>
-    <t>45,416,291.0</t>
-  </si>
-  <si>
-    <t>33,453,457.2</t>
-  </si>
-  <si>
-    <t>30,989,023.3</t>
-  </si>
-  <si>
-    <t>139,106,057.0</t>
-  </si>
-  <si>
-    <t>40,893,272.79</t>
-  </si>
-  <si>
-    <t>28,442,118.9</t>
-  </si>
-  <si>
-    <t>24,795,586.6</t>
-  </si>
-  <si>
-    <t>14,240,728.4</t>
-  </si>
-  <si>
-    <t>230,646,498.1</t>
-  </si>
-  <si>
-    <t>226,390,421.4</t>
-  </si>
-  <si>
-    <t>28,630,089.8</t>
-  </si>
-  <si>
-    <t>25,837,173.1</t>
-  </si>
-  <si>
-    <t>21,215,206.7</t>
-  </si>
-  <si>
-    <t>48,534,782.3</t>
-  </si>
-  <si>
-    <t>37,717,608.5</t>
-  </si>
-  <si>
-    <t>26,527,572.3</t>
-  </si>
-  <si>
-    <t>7,784,201.6</t>
-  </si>
-  <si>
-    <t>5,146,396.09</t>
-  </si>
-  <si>
-    <t>183,352,435.1</t>
-  </si>
-  <si>
-    <t>142,694,895.5</t>
-  </si>
-  <si>
-    <t>54,444,769.5</t>
-  </si>
-  <si>
-    <t>43,846,484.9</t>
-  </si>
-  <si>
-    <t>42,635,232.29</t>
-  </si>
-  <si>
-    <t>477,748,112.5</t>
-  </si>
-  <si>
-    <t>255,487,107.4</t>
-  </si>
-  <si>
-    <t>86,240,559.7</t>
-  </si>
-  <si>
-    <t>85,218,393.09</t>
-  </si>
-  <si>
-    <t>34,929,009.9</t>
-  </si>
-  <si>
-    <t>42,475,282.7</t>
-  </si>
-  <si>
-    <t>40,827,748.7</t>
-  </si>
-  <si>
-    <t>22,350,815.6</t>
-  </si>
-  <si>
-    <t>18,189,184.7</t>
-  </si>
-  <si>
-    <t>17,935,017.7</t>
-  </si>
-  <si>
-    <t>288,883,807.39</t>
-  </si>
-  <si>
-    <t>81,868,354.9</t>
-  </si>
-  <si>
-    <t>39,519,051.4</t>
-  </si>
-  <si>
-    <t>32,039,955.1</t>
-  </si>
-  <si>
-    <t>28,321,355.8</t>
-  </si>
-  <si>
-    <t>349,635,969.0</t>
-  </si>
-  <si>
-    <t>130,338,382.5</t>
-  </si>
-  <si>
-    <t>24,612,011.3</t>
-  </si>
-  <si>
-    <t>12,250,509.4</t>
-  </si>
-  <si>
-    <t>11,648,906.4</t>
-  </si>
-  <si>
-    <t>65,414,147.0</t>
-  </si>
-  <si>
-    <t>51,896,998.6</t>
-  </si>
-  <si>
-    <t>31,399,221.9</t>
-  </si>
-  <si>
-    <t>25,426,697.2</t>
-  </si>
-  <si>
-    <t>20,857,398.39</t>
-  </si>
-  <si>
-    <t>530,323,465.0</t>
-  </si>
-  <si>
-    <t>36,069,119.0</t>
-  </si>
-  <si>
-    <t>22,469,944.3</t>
-  </si>
-  <si>
-    <t>14,723,314.8</t>
-  </si>
-  <si>
-    <t>10,740,243.0</t>
+    <t>191,439,357.7</t>
+  </si>
+  <si>
+    <t>185,734,236.2</t>
+  </si>
+  <si>
+    <t>140,560,616.3</t>
+  </si>
+  <si>
+    <t>84,518,307.8</t>
+  </si>
+  <si>
+    <t>50,468,336.3</t>
+  </si>
+  <si>
+    <t>212,105,455.9</t>
+  </si>
+  <si>
+    <t>104,774,212.8</t>
+  </si>
+  <si>
+    <t>40,184,410.7</t>
+  </si>
+  <si>
+    <t>38,461,874.7</t>
+  </si>
+  <si>
+    <t>31,230,191.8</t>
+  </si>
+  <si>
+    <t>148,682,789.1</t>
+  </si>
+  <si>
+    <t>115,784,021.3</t>
+  </si>
+  <si>
+    <t>51,153,199.4</t>
+  </si>
+  <si>
+    <t>34,114,640.7</t>
+  </si>
+  <si>
+    <t>28,149,864.9</t>
+  </si>
+  <si>
+    <t>96,697,739.4</t>
+  </si>
+  <si>
+    <t>86,226,384.1</t>
+  </si>
+  <si>
+    <t>79,168,752.09</t>
+  </si>
+  <si>
+    <t>33,118,493.9</t>
+  </si>
+  <si>
+    <t>30,480,034.7</t>
+  </si>
+  <si>
+    <t>137,149,320.9</t>
+  </si>
+  <si>
+    <t>87,847,872.8</t>
+  </si>
+  <si>
+    <t>47,783,335.0</t>
+  </si>
+  <si>
+    <t>46,677,751.2</t>
+  </si>
+  <si>
+    <t>22,276,891.4</t>
+  </si>
+  <si>
+    <t>108,519,773.4</t>
+  </si>
+  <si>
+    <t>89,877,954.7</t>
+  </si>
+  <si>
+    <t>33,164,315.2</t>
+  </si>
+  <si>
+    <t>26,166,533.1</t>
+  </si>
+  <si>
+    <t>21,810,811.8</t>
+  </si>
+  <si>
+    <t>123,711,403.4</t>
+  </si>
+  <si>
+    <t>66,960,684.6</t>
+  </si>
+  <si>
+    <t>37,193,508.5</t>
+  </si>
+  <si>
+    <t>16,448,760.8</t>
+  </si>
+  <si>
+    <t>15,202,807.8</t>
+  </si>
+  <si>
+    <t>291,083,479.39</t>
+  </si>
+  <si>
+    <t>163,094,060.69</t>
+  </si>
+  <si>
+    <t>69,264,153.59</t>
+  </si>
+  <si>
+    <t>61,599,075.0</t>
+  </si>
+  <si>
+    <t>55,094,402.6</t>
+  </si>
+  <si>
+    <t>112,889,974.8</t>
+  </si>
+  <si>
+    <t>72,811,604.09</t>
+  </si>
+  <si>
+    <t>54,143,411.1</t>
+  </si>
+  <si>
+    <t>33,159,571.1</t>
+  </si>
+  <si>
+    <t>27,654,859.1</t>
+  </si>
+  <si>
+    <t>131,723,495.6</t>
+  </si>
+  <si>
+    <t>85,614,704.25</t>
+  </si>
+  <si>
+    <t>41,364,669.4</t>
+  </si>
+  <si>
+    <t>28,688,562.5</t>
+  </si>
+  <si>
+    <t>27,465,482.7</t>
+  </si>
+  <si>
+    <t>105,157,998.6</t>
+  </si>
+  <si>
+    <t>88,767,981.3</t>
+  </si>
+  <si>
+    <t>41,058,315.1</t>
+  </si>
+  <si>
+    <t>35,815,300.9</t>
+  </si>
+  <si>
+    <t>34,630,471.6</t>
+  </si>
+  <si>
+    <t>117,238,505.4</t>
+  </si>
+  <si>
+    <t>63,738,609.0</t>
+  </si>
+  <si>
+    <t>38,342,109.0</t>
+  </si>
+  <si>
+    <t>30,101,177.7</t>
+  </si>
+  <si>
+    <t>28,771,893.1</t>
+  </si>
+  <si>
+    <t>96,124,002.2</t>
+  </si>
+  <si>
+    <t>78,468,868.59</t>
+  </si>
+  <si>
+    <t>53,777,882.8</t>
+  </si>
+  <si>
+    <t>41,343,093.1</t>
+  </si>
+  <si>
+    <t>32,976,564.9</t>
+  </si>
+  <si>
+    <t>165,302,827.6</t>
+  </si>
+  <si>
+    <t>81,580,061.0</t>
+  </si>
+  <si>
+    <t>29,451,917.1</t>
+  </si>
+  <si>
+    <t>22,589,941.2</t>
+  </si>
+  <si>
+    <t>21,767,911.3</t>
   </si>
 </sst>
 </file>
@@ -1696,34 +1657,34 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.2122277442541624</v>
+        <v>0.04445328727577214</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>65</v>
-      </c>
       <c r="G9" s="12">
-        <v>0.0319665723106933</v>
+        <v>0.04410586807103006</v>
       </c>
       <c r="H9" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="J9" s="14">
-        <v>0.5151028760186611</v>
+        <v>0.01680102000255775</v>
       </c>
       <c r="K9" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="L9" s="15" t="s">
-        <v>84</v>
-      </c>
       <c r="M9" s="16">
-        <v>0.0833659753963074</v>
+        <v>0.05357049003296564</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>92</v>
@@ -1732,25 +1693,25 @@
         <v>93</v>
       </c>
       <c r="P9" s="18">
-        <v>0.07679849758475382</v>
+        <v>0.03345334938271986</v>
       </c>
       <c r="Q9" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="R9" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="R9" s="15" t="s">
-        <v>102</v>
-      </c>
       <c r="S9" s="16">
-        <v>0.1359453814050372</v>
+        <v>0.01389501951695367</v>
       </c>
       <c r="T9" s="17" t="s">
         <v>109</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="V9" s="18">
-        <v>0.03474797639123676</v>
+        <v>0.04934149420006362</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1762,34 +1723,34 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.05286954711499513</v>
+        <v>0.04093390530688121</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="G10" s="12">
-        <v>0.01284244457037097</v>
+        <v>0.02720050055694904</v>
       </c>
       <c r="H10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="13" t="s">
-        <v>77</v>
-      </c>
       <c r="J10" s="14">
-        <v>0.05387049511193292</v>
+        <v>0.01236961926378076</v>
       </c>
       <c r="K10" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="L10" s="15" t="s">
-        <v>86</v>
-      </c>
       <c r="M10" s="16">
-        <v>0.03901760603621848</v>
+        <v>0.03105978803541102</v>
       </c>
       <c r="N10" s="17" t="s">
         <v>94</v>
@@ -1798,25 +1759,25 @@
         <v>95</v>
       </c>
       <c r="P10" s="18">
-        <v>0.04040532606719936</v>
+        <v>0.01356917250521929</v>
       </c>
       <c r="Q10" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="R10" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="R10" s="15" t="s">
-        <v>104</v>
-      </c>
       <c r="S10" s="16">
-        <v>0.07160685543669779</v>
+        <v>0.01326994033372434</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V10" s="18">
-        <v>0.02986290533267599</v>
+        <v>0.01539995425772956</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1828,61 +1789,61 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.04287453130481025</v>
+        <v>0.01818818931063372</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" s="12">
-        <v>0.01079712798192333</v>
+        <v>0.01671191181307026</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.02982293712100316</v>
+        <v>0.01233582187675338</v>
       </c>
       <c r="K11" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="L11" s="15" t="s">
-        <v>88</v>
-      </c>
       <c r="M11" s="16">
-        <v>0.02897119518676188</v>
+        <v>0.03066970241700855</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P11" s="18">
-        <v>0.03535769330785505</v>
+        <v>0.01234753042974021</v>
       </c>
       <c r="Q11" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="R11" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="R11" s="15" t="s">
-        <v>106</v>
-      </c>
       <c r="S11" s="16">
-        <v>0.05538504356251082</v>
+        <v>0.01075607096165291</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="V11" s="18">
-        <v>0.01743914065135195</v>
+        <v>0.01301790459421188</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1894,61 +1855,61 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.03874215400145246</v>
+        <v>0.01808643755085524</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>71</v>
-      </c>
       <c r="G12" s="12">
-        <v>0.01029010139968943</v>
+        <v>0.01219834389408436</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.02963412091176201</v>
+        <v>0.01204444611963806</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="L12" s="15" t="s">
         <v>89</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02498095914122684</v>
+        <v>0.02189722352126006</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="O12" s="17" t="s">
         <v>98</v>
       </c>
       <c r="P12" s="18">
-        <v>0.006821581901837916</v>
+        <v>0.01194821357854649</v>
       </c>
       <c r="Q12" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="R12" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="R12" s="15" t="s">
-        <v>108</v>
-      </c>
       <c r="S12" s="16">
-        <v>0.03343451106735746</v>
+        <v>0.01070419440601611</v>
       </c>
       <c r="T12" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="U12" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="U12" s="17" t="s">
-        <v>115</v>
-      </c>
       <c r="V12" s="18">
-        <v>0.01462729833296717</v>
+        <v>0.0126701501655976</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1960,25 +1921,25 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02168786684797767</v>
+        <v>0.01641880924775517</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="G13" s="12">
-        <v>0.008550627162878277</v>
+        <v>0.01070490250568754</v>
       </c>
       <c r="H13" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="I13" s="13" t="s">
-        <v>82</v>
-      </c>
       <c r="J13" s="14">
-        <v>0.01945226303768031</v>
+        <v>0.01192818844141457</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>90</v>
@@ -1987,7 +1948,7 @@
         <v>91</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02269172912175014</v>
+        <v>0.02145825984949335</v>
       </c>
       <c r="N13" s="17" t="s">
         <v>99</v>
@@ -1996,25 +1957,25 @@
         <v>100</v>
       </c>
       <c r="P13" s="18">
-        <v>0.006481842942139356</v>
+        <v>0.01140726691900394</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S13" s="16">
-        <v>0.03295313808474991</v>
+        <v>0.009912690437675427</v>
       </c>
       <c r="T13" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="U13" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="U13" s="17" t="s">
-        <v>117</v>
-      </c>
       <c r="V13" s="18">
-        <v>0.01067756037401683</v>
+        <v>0.01018338451695998</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2025,7 +1986,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -2034,7 +1995,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2043,7 +2004,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2052,7 +2013,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2061,7 +2022,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2070,7 +2031,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2079,7 +2040,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2088,566 +2049,566 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D16" s="10">
-        <v>0.0550448053338137</v>
+        <v>0.03656932548471049</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G16" s="12">
-        <v>0.2588347696012919</v>
+        <v>0.01312691374301263</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J16" s="14">
-        <v>0.0177602288867639</v>
+        <v>0.01880872103186016</v>
       </c>
       <c r="K16" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0.03487037397638208</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="O16" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="L16" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="M16" s="16">
-        <v>0.1539915675615879</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="O16" s="17" t="s">
-        <v>153</v>
-      </c>
       <c r="P16" s="18">
-        <v>0.2817876045850859</v>
+        <v>0.02900592725266709</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="S16" s="16">
-        <v>0.01955485738951198</v>
+        <v>0.01386037372666599</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="V16" s="18">
-        <v>0.6734170766210844</v>
+        <v>0.0747304344699426</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D17" s="10">
-        <v>0.03131304756559453</v>
+        <v>0.01682248863624851</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G17" s="12">
-        <v>0.1967848985590645</v>
+        <v>0.01214579557586328</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="J17" s="14">
-        <v>0.01085129965126991</v>
+        <v>0.01725850151254251</v>
       </c>
       <c r="K17" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="M17" s="16">
+        <v>0.02437504283733908</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="O17" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="L17" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="M17" s="16">
-        <v>0.05580395830779337</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="O17" s="17" t="s">
-        <v>155</v>
-      </c>
       <c r="P17" s="18">
-        <v>0.09805732307786261</v>
+        <v>0.01518502186886305</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="S17" s="16">
-        <v>0.01209976872387206</v>
+        <v>0.01230577030620978</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="V17" s="18">
-        <v>0.04531736844839534</v>
+        <v>0.01505815343205508</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D18" s="10">
-        <v>0.01846415710322916</v>
+        <v>0.01644511934518482</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G18" s="12">
-        <v>0.06370163490673854</v>
+        <v>0.01064690243852066</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J18" s="14">
-        <v>0.00993207980688429</v>
+        <v>0.01305503055216244</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>148</v>
+        <v>88</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="M18" s="16">
-        <v>0.05443110494019224</v>
+        <v>0.0240755779248966</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>156</v>
+        <v>67</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="P18" s="18">
-        <v>0.06629024220143327</v>
+        <v>0.01401216383852876</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="S18" s="16">
-        <v>0.01027352761107292</v>
+        <v>0.0119773167818756</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="V18" s="18">
-        <v>0.02200122025215469</v>
+        <v>0.01271710571740469</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D19" s="10">
-        <v>0.01551937195284713</v>
+        <v>0.01512346834455947</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G19" s="12">
-        <v>0.04957973794861253</v>
+        <v>0.01031025779060684</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="I19" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="J19" s="14">
+        <v>0.01263297630061101</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="L19" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="J19" s="14">
-        <v>0.008079416757225866</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>150</v>
-      </c>
       <c r="M19" s="16">
-        <v>0.04469578523747543</v>
+        <v>0.02320713288338862</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="P19" s="18">
-        <v>0.02196902149929556</v>
+        <v>0.01145371718154117</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="S19" s="16">
-        <v>0.007884178297947362</v>
+        <v>0.01170497265771613</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>174</v>
+        <v>65</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01228132096563359</v>
+        <v>0.01247677186845921</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01502420066019929</v>
+        <v>0.01440002089958378</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G20" s="12">
-        <v>0.03428940662117689</v>
+        <v>0.01000106392683239</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="I20" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.008774598384471829</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="L20" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="J20" s="14">
-        <v>0.006651491506267196</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>151</v>
-      </c>
       <c r="M20" s="16">
-        <v>0.02510559623024117</v>
+        <v>0.01578566964814207</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01772171409435206</v>
+        <v>0.009503603434146517</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="S20" s="16">
-        <v>0.007840148213675764</v>
+        <v>0.01090159530622383</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>176</v>
+        <v>71</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="V20" s="18">
-        <v>0.007702483340398004</v>
+        <v>0.01079020705226943</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>152</v>
+        <v>54</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2692202155215402</v>
+        <v>0.3064946421881774</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2538379576747878</v>
+        <v>0.2128148416663087</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D33" s="22">
-        <v>0.08727241084964869</v>
+        <v>0.1025159875955561</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="D34" s="22">
-        <v>0.08178812357398052</v>
+        <v>0.08282398254603247</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="D35" s="22">
-        <v>0.07066803228996678</v>
+        <v>0.07165621630447236</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="D36" s="22">
-        <v>0.0613342668567391</v>
+        <v>0.06489942468603498</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="D37" s="22">
-        <v>0.05215828157216201</v>
+        <v>0.05189786613141705</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="D38" s="22">
-        <v>0.04293111149788112</v>
+        <v>0.02979851992805881</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="D39" s="22">
-        <v>0.0210171164824781</v>
+        <v>0.02271996727843679</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01854736644796046</v>
+        <v>0.02143675477160645</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01134459732563562</v>
+        <v>0.01718424730411482</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="D42" s="22">
-        <v>0.003437519083661038</v>
+        <v>0.007713999568853732</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="D43" s="22">
-        <v>0.002856340309260204</v>
+        <v>0.005640213837227319</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="D44" s="22">
-        <v>0.001437879420426071</v>
+        <v>0.001842060968800368</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="D45" s="22">
-        <v>0.0003153502015974449</v>
+        <v>0.0005612752249027511</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -3026,331 +2987,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="D9" s="10">
-        <v>0.2725736676548707</v>
+        <v>0.1221957872087272</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="G9" s="12">
-        <v>0.06365261883864254</v>
+        <v>0.2324920472890392</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="J9" s="14">
-        <v>0.5166223518929153</v>
+        <v>0.1731326902280144</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1555116290348207</v>
+        <v>0.1160581191274505</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1659464744014031</v>
+        <v>0.1672729029284064</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="S9" s="16">
-        <v>0.2773331352966324</v>
+        <v>0.1503444277452674</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="V9" s="18">
-        <v>0.06164055078633829</v>
+        <v>0.17575730801511</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1261954475899628</v>
+        <v>0.1185542068085964</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="G10" s="12">
-        <v>0.04562587937235964</v>
+        <v>0.1148446235558124</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="J10" s="14">
-        <v>0.07025089334822991</v>
+        <v>0.1348239376892797</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="M10" s="16">
-        <v>0.05597492265544701</v>
+        <v>0.103490236895932</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="P10" s="18">
-        <v>0.04878360147822171</v>
+        <v>0.1071428469562432</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="S10" s="16">
-        <v>0.2722155588105494</v>
+        <v>0.1245178573722175</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="V10" s="18">
-        <v>0.04790243310277452</v>
+        <v>0.09513132455617129</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="D11" s="10">
-        <v>0.1134211335534185</v>
+        <v>0.08971987456329805</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="G11" s="12">
-        <v>0.02478833499975757</v>
+        <v>0.04404674963736552</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="J11" s="14">
-        <v>0.0686830122256181</v>
+        <v>0.05956500466194208</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="M11" s="16">
-        <v>0.04804832801459195</v>
+        <v>0.0950195580517717</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="P11" s="18">
-        <v>0.03393000605257982</v>
+        <v>0.0582785033465705</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="S11" s="16">
-        <v>0.03442528992838038</v>
+        <v>0.04594618873676779</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="V11" s="18">
-        <v>0.0336907695905419</v>
+        <v>0.05284097302219361</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="D12" s="10">
-        <v>0.04994908940996085</v>
+        <v>0.05394805581909088</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01584288863986622</v>
+        <v>0.0421586514766191</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="J12" s="14">
-        <v>0.06608159575986804</v>
+        <v>0.03972456769411727</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="M12" s="16">
-        <v>0.03539220507389546</v>
+        <v>0.03974932748394675</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="P12" s="18">
-        <v>0.02957987786962198</v>
+        <v>0.05693008827281697</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="S12" s="16">
-        <v>0.03106704104355449</v>
+        <v>0.03625138831147889</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="V12" s="18">
-        <v>0.009886156923297784</v>
+        <v>0.02336882323648805</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="D13" s="10">
-        <v>0.03204745320943048</v>
+        <v>0.03221395097322394</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01188910093154065</v>
+        <v>0.03423189280069511</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="J13" s="14">
-        <v>0.02770346223294926</v>
+        <v>0.03277892397091275</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="M13" s="16">
-        <v>0.03278494838713784</v>
+        <v>0.03658260803376572</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="P13" s="18">
-        <v>0.0169884670865765</v>
+        <v>0.02716980491223745</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02550951277624068</v>
+        <v>0.03021692651940909</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="V13" s="18">
-        <v>0.006536069085626934</v>
+        <v>0.02159869260038737</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3361,7 +3322,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3370,7 +3331,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3379,7 +3340,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3388,7 +3349,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3397,7 +3358,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3406,7 +3367,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3415,7 +3376,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3424,331 +3385,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1221856287414316</v>
+        <v>0.1857986536106014</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="G16" s="12">
-        <v>0.3973828463630469</v>
+        <v>0.1237404349091053</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="J16" s="14">
-        <v>0.0442335096373658</v>
+        <v>0.1533845530979888</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="M16" s="16">
-        <v>0.3056256605379644</v>
+        <v>0.1262122527832648</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="P16" s="18">
-        <v>0.4170979871815954</v>
+        <v>0.142988860641494</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="S16" s="16">
-        <v>0.07865504410302947</v>
+        <v>0.1331711968294971</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="V16" s="18">
-        <v>0.67352584947145</v>
+        <v>0.2348464182588185</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="D17" s="10">
-        <v>0.09509154059149103</v>
+        <v>0.1041029774427854</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="G17" s="12">
-        <v>0.2125098797699038</v>
+        <v>0.07980991734408281</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="J17" s="14">
-        <v>0.04251777741772155</v>
+        <v>0.09969347602101389</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="M17" s="16">
-        <v>0.08661291980558754</v>
+        <v>0.1065407010788785</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1554870831760873</v>
+        <v>0.07773820596474165</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="S17" s="16">
-        <v>0.06240180298762986</v>
+        <v>0.1087115903016213</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="V17" s="18">
-        <v>0.04580880465879785</v>
+        <v>0.1159011337274059</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D18" s="10">
-        <v>0.03628186551987504</v>
+        <v>0.0442113255925231</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="G18" s="12">
-        <v>0.07173344737291511</v>
+        <v>0.05934742432927249</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="J18" s="14">
-        <v>0.02327600793686032</v>
+        <v>0.04816681565475438</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="M18" s="16">
-        <v>0.04180932222080221</v>
+        <v>0.0492788234204387</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="P18" s="18">
-        <v>0.02936088184256775</v>
+        <v>0.04676359922703325</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="S18" s="16">
-        <v>0.03775493981975044</v>
+        <v>0.0745044406342085</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="V18" s="18">
-        <v>0.02853746688774872</v>
+        <v>0.04184246175466299</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="D19" s="10">
-        <v>0.02921919374938362</v>
+        <v>0.03931870411281904</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="G19" s="12">
-        <v>0.07088322638336543</v>
+        <v>0.03634671507884328</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01894210998914143</v>
+        <v>0.03340620682773787</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="M19" s="16">
-        <v>0.03389678545563306</v>
+        <v>0.04298607686414728</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01461423670826388</v>
+        <v>0.03671262345596354</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="S19" s="16">
-        <v>0.03057347808357687</v>
+        <v>0.05727715308092243</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01869902759762963</v>
+        <v>0.03209362390542263</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="D20" s="10">
-        <v>0.02841201788387097</v>
+        <v>0.03516677018448618</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="G20" s="12">
-        <v>0.02905336308305152</v>
+        <v>0.03031291572565776</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01867742196991372</v>
+        <v>0.03198199964532403</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="M20" s="16">
-        <v>0.02996267998406929</v>
+        <v>0.04156402645326567</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01389655482587606</v>
+        <v>0.0350913737669319</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="S20" s="16">
-        <v>0.02507927820302321</v>
+        <v>0.04568607750977087</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01364041338450825</v>
+        <v>0.03092576258980256</v>
       </c>
     </row>
   </sheetData>
